--- a/Design Files/Baseboard-v3.1/BOM/JLCPCB-BOM-Baseboard-v3.1-Development.xlsx
+++ b/Design Files/Baseboard-v3.1/BOM/JLCPCB-BOM-Baseboard-v3.1-Development.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\chrisbyrd-esp32iotproduct\Design Files\Baseboard-v3.1\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="495">
   <si>
     <t>Comment</t>
   </si>
@@ -683,15 +688,9 @@
     <t>-</t>
   </si>
   <si>
-    <t>AFC01-S15FCC-00</t>
-  </si>
-  <si>
     <t>J18</t>
   </si>
   <si>
-    <t>DNP</t>
-  </si>
-  <si>
     <t>POGO Connector 6 Pin</t>
   </si>
   <si>
@@ -1517,21 +1516,14 @@
     <t>C2890594</t>
   </si>
   <si>
-    <t xml:space="preserve">Antenna 2.4GHz w/ MMCX mini-OmniDirectional WiFi, BlueTooth
-</t>
+    <t>N091-2832TSWFG05-C15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1554,172 +1546,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1744,194 +1577,8 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1940,444 +1587,59 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2635,2180 +1897,2166 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:D153"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="19.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="26.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="48" spans="1:4">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:4" ht="48">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="24" spans="1:4">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:4" ht="24">
+      <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" ht="24" spans="1:4">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:4" ht="24">
+      <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="3" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="52" ht="24" spans="1:4">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:4" ht="24">
+      <c r="A52" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="3" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="3" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="3" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="3" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="36">
+      <c r="A95" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="24">
+      <c r="A102" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="24">
+      <c r="A113" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="96" ht="36" spans="1:4">
-      <c r="A96" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="103" ht="24" spans="1:4">
-      <c r="A103" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="114" ht="24" spans="1:4">
-      <c r="A114" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="C150" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="D152" s="6" t="s">
+      <c r="C153" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D153" s="3" t="s">
         <v>493</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="154" ht="60" spans="1:4">
-      <c r="A154" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C154" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="D154" s="10" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>